--- a/docs/Schedule2026.xlsx
+++ b/docs/Schedule2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhouy\Documents\KU2026Seminar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C421D06B-7CDC-4736-AEEA-CE32505E456E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88604644-7F80-472F-A80F-35FD5F1BDC39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{F3CF7C89-0ED2-43E9-981B-1B551F77510C}"/>
+    <workbookView xWindow="-28920" yWindow="5235" windowWidth="29040" windowHeight="15720" xr2:uid="{F3CF7C89-0ED2-43E9-981B-1B551F77510C}"/>
   </bookViews>
   <sheets>
     <sheet name="B" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="124">
   <si>
     <t>Chapter</t>
   </si>
@@ -107,9 +107,6 @@
     <t>One-way ANOVA</t>
   </si>
   <si>
-    <t>Hierachical model</t>
-  </si>
-  <si>
     <t>Order statistics</t>
   </si>
   <si>
@@ -180,9 +177,6 @@
   </si>
   <si>
     <t>Sufficiency principle</t>
-  </si>
-  <si>
-    <t>Sufficiency principle, EM algorithm</t>
   </si>
   <si>
     <t>https://elib.maruzen.co.jp/elib/html/BookDetail/Id/3000068387</t>
@@ -412,6 +406,9 @@
   </si>
   <si>
     <t>268de05d@stu.kobe-u.ac.jp</t>
+  </si>
+  <si>
+    <t>Hierachical model, EM algorithm</t>
   </si>
 </sst>
 </file>
@@ -672,6 +669,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -686,12 +689,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1059,13 +1056,13 @@
         <v>5</v>
       </c>
       <c r="D1" s="33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E1" s="33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F1" s="29" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
@@ -1077,22 +1074,22 @@
         <v>4</v>
       </c>
       <c r="J1" s="41" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K1" s="34" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L1" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="M1" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="M1" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="O1" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.4">
@@ -1110,7 +1107,7 @@
       </c>
       <c r="E2" s="8"/>
       <c r="F2" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>8</v>
@@ -1119,28 +1116,28 @@
         <v>19</v>
       </c>
       <c r="I2" s="30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J2" s="42" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K2" s="46" t="s">
-        <v>112</v>
-      </c>
-      <c r="L2" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="M2" s="47" t="s">
+        <v>110</v>
+      </c>
+      <c r="L2" s="50" t="s">
         <v>66</v>
       </c>
+      <c r="M2" s="49" t="s">
+        <v>64</v>
+      </c>
       <c r="N2" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.4">
@@ -1154,7 +1151,7 @@
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>8</v>
@@ -1163,22 +1160,22 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I3" s="30" t="s">
-        <v>23</v>
+        <v>123</v>
       </c>
       <c r="J3" s="42" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K3" s="46"/>
-      <c r="L3" s="49"/>
-      <c r="M3" s="47"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="49"/>
       <c r="N3" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.4">
@@ -1192,7 +1189,7 @@
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>8</v>
@@ -1201,22 +1198,22 @@
         <v>5.4</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J4" s="42" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K4" s="46"/>
-      <c r="L4" s="49"/>
-      <c r="M4" s="47"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="49"/>
       <c r="N4" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.4">
@@ -1230,7 +1227,7 @@
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>8</v>
@@ -1239,22 +1236,22 @@
         <v>5.6</v>
       </c>
       <c r="I5" s="30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J5" s="42" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K5" s="46"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="47"/>
+      <c r="L5" s="51"/>
+      <c r="M5" s="49"/>
       <c r="N5" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.4">
@@ -1270,31 +1267,31 @@
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>8</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I6" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="J6" s="53" t="s">
-        <v>101</v>
+        <v>46</v>
+      </c>
+      <c r="J6" s="47" t="s">
+        <v>99</v>
       </c>
       <c r="K6" s="46"/>
-      <c r="L6" s="49"/>
-      <c r="M6" s="47"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="49"/>
       <c r="N6" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O6" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="P6" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.4">
@@ -1308,23 +1305,23 @@
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" s="53"/>
+        <v>46</v>
+      </c>
+      <c r="J7" s="47"/>
       <c r="K7" s="46"/>
-      <c r="L7" s="49"/>
-      <c r="M7" s="47"/>
+      <c r="L7" s="51"/>
+      <c r="M7" s="49"/>
       <c r="O7" s="11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="P7" s="3"/>
     </row>
@@ -1339,23 +1336,23 @@
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>8</v>
       </c>
       <c r="H8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="I8" s="30" t="s">
-        <v>27</v>
-      </c>
       <c r="J8" s="42" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K8" s="46"/>
-      <c r="L8" s="49"/>
-      <c r="M8" s="47"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="49"/>
       <c r="P8" s="3"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.4">
@@ -1369,7 +1366,7 @@
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>8</v>
@@ -1378,22 +1375,22 @@
         <v>20</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J9" s="42" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K9" s="46"/>
-      <c r="L9" s="49"/>
-      <c r="M9" s="47"/>
+      <c r="L9" s="51"/>
+      <c r="M9" s="49"/>
       <c r="N9" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="Q9" s="27"/>
     </row>
@@ -1410,7 +1407,7 @@
       </c>
       <c r="E10" s="14"/>
       <c r="F10" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>3</v>
@@ -1422,23 +1419,23 @@
         <v>22</v>
       </c>
       <c r="J10" s="46" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K10" s="46" t="s">
-        <v>118</v>
-      </c>
-      <c r="L10" s="50" t="s">
-        <v>49</v>
-      </c>
-      <c r="M10" s="47"/>
+        <v>116</v>
+      </c>
+      <c r="L10" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="M10" s="49"/>
       <c r="N10" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="O10" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="P10" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="Q10" s="27"/>
     </row>
@@ -1453,23 +1450,23 @@
       </c>
       <c r="E11" s="14"/>
       <c r="F11" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>3</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J11" s="46"/>
       <c r="K11" s="46"/>
-      <c r="L11" s="50"/>
-      <c r="M11" s="47"/>
+      <c r="L11" s="52"/>
+      <c r="M11" s="49"/>
       <c r="P11" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.4">
@@ -1483,28 +1480,28 @@
       </c>
       <c r="E12" s="14"/>
       <c r="F12" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>3</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J12" s="46" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K12" s="46"/>
-      <c r="L12" s="50"/>
-      <c r="M12" s="47"/>
+      <c r="L12" s="52"/>
+      <c r="M12" s="49"/>
       <c r="O12" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.4">
@@ -1518,21 +1515,21 @@
       </c>
       <c r="E13" s="14"/>
       <c r="F13" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G13" s="12" t="s">
         <v>3</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>6</v>
       </c>
       <c r="J13" s="46"/>
       <c r="K13" s="46"/>
-      <c r="L13" s="50"/>
-      <c r="M13" s="47"/>
+      <c r="L13" s="52"/>
+      <c r="M13" s="49"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A14" s="12">
@@ -1547,21 +1544,21 @@
       </c>
       <c r="E14" s="14"/>
       <c r="F14" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>6</v>
       </c>
       <c r="J14" s="46"/>
       <c r="K14" s="46"/>
-      <c r="L14" s="50"/>
-      <c r="M14" s="47"/>
+      <c r="L14" s="52"/>
+      <c r="M14" s="49"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A15" s="12">
@@ -1574,23 +1571,23 @@
       </c>
       <c r="E15" s="14"/>
       <c r="F15" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>3</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>7</v>
       </c>
       <c r="J15" s="46" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K15" s="46"/>
-      <c r="L15" s="50"/>
-      <c r="M15" s="47"/>
+      <c r="L15" s="52"/>
+      <c r="M15" s="49"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A16" s="12">
@@ -1603,21 +1600,21 @@
       </c>
       <c r="E16" s="14"/>
       <c r="F16" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>3</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I16" s="13" t="s">
         <v>7</v>
       </c>
       <c r="J16" s="46"/>
       <c r="K16" s="46"/>
-      <c r="L16" s="50"/>
-      <c r="M16" s="47"/>
+      <c r="L16" s="52"/>
+      <c r="M16" s="49"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A17" s="12">
@@ -1630,21 +1627,21 @@
       </c>
       <c r="E17" s="14"/>
       <c r="F17" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>3</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J17" s="46"/>
       <c r="K17" s="46"/>
-      <c r="L17" s="50"/>
-      <c r="M17" s="47"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="49"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A18" s="12">
@@ -1659,21 +1656,21 @@
       </c>
       <c r="E18" s="14"/>
       <c r="F18" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>3</v>
       </c>
       <c r="H18" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I18" s="13" t="s">
         <v>37</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>38</v>
       </c>
       <c r="J18" s="46"/>
       <c r="K18" s="46"/>
-      <c r="L18" s="50"/>
-      <c r="M18" s="47"/>
+      <c r="L18" s="52"/>
+      <c r="M18" s="49"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A19" s="16">
@@ -1686,24 +1683,24 @@
       </c>
       <c r="E19" s="18"/>
       <c r="F19" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G19" s="16" t="s">
         <v>9</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I19" s="17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J19" s="41" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K19" s="46" t="s">
-        <v>119</v>
-      </c>
-      <c r="M19" s="47"/>
+        <v>117</v>
+      </c>
+      <c r="M19" s="49"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A20" s="16">
@@ -1716,22 +1713,22 @@
       </c>
       <c r="E20" s="18"/>
       <c r="F20" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G20" s="16" t="s">
         <v>9</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J20" s="41" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K20" s="46"/>
-      <c r="M20" s="47"/>
+      <c r="M20" s="49"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A21" s="16">
@@ -1744,19 +1741,19 @@
       </c>
       <c r="E21" s="18"/>
       <c r="F21" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G21" s="16" t="s">
         <v>9</v>
       </c>
       <c r="H21" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="I21" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="J21" s="41" t="s">
         <v>86</v>
-      </c>
-      <c r="I21" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="J21" s="41" t="s">
-        <v>88</v>
       </c>
       <c r="K21" s="46"/>
     </row>
@@ -1805,23 +1802,23 @@
       </c>
       <c r="E24" s="18"/>
       <c r="F24" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G24" s="16" t="s">
         <v>9</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J24" s="46" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K24" s="46"/>
-      <c r="M24" s="47" t="s">
-        <v>67</v>
+      <c r="M24" s="49" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.4">
@@ -1835,20 +1832,20 @@
       </c>
       <c r="E25" s="18"/>
       <c r="F25" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G25" s="16" t="s">
         <v>9</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I25" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J25" s="46"/>
       <c r="K25" s="46"/>
-      <c r="M25" s="47"/>
+      <c r="M25" s="49"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A26" s="16">
@@ -1861,7 +1858,7 @@
       </c>
       <c r="E26" s="18"/>
       <c r="F26" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G26" s="16" t="s">
         <v>9</v>
@@ -1870,13 +1867,13 @@
         <v>7</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J26" s="46" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K26" s="46"/>
-      <c r="M26" s="47"/>
+      <c r="M26" s="49"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A27" s="16">
@@ -1889,7 +1886,7 @@
       </c>
       <c r="E27" s="18"/>
       <c r="F27" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G27" s="16" t="s">
         <v>9</v>
@@ -1898,11 +1895,11 @@
         <v>7</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J27" s="46"/>
       <c r="K27" s="46"/>
-      <c r="M27" s="47"/>
+      <c r="M27" s="49"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A28" s="16">
@@ -1917,7 +1914,7 @@
       </c>
       <c r="E28" s="18"/>
       <c r="F28" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G28" s="16" t="s">
         <v>9</v>
@@ -1926,13 +1923,13 @@
         <v>8</v>
       </c>
       <c r="I28" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J28" s="46" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K28" s="46"/>
-      <c r="M28" s="47"/>
+      <c r="M28" s="49"/>
     </row>
     <row r="29" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="16">
@@ -1945,7 +1942,7 @@
       </c>
       <c r="E29" s="18"/>
       <c r="F29" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G29" s="16" t="s">
         <v>9</v>
@@ -1954,11 +1951,11 @@
         <v>8</v>
       </c>
       <c r="I29" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J29" s="46"/>
       <c r="K29" s="46"/>
-      <c r="M29" s="47"/>
+      <c r="M29" s="49"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A30" s="16">
@@ -1971,7 +1968,7 @@
       </c>
       <c r="E30" s="18"/>
       <c r="F30" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G30" s="16" t="s">
         <v>9</v>
@@ -1980,14 +1977,14 @@
         <v>9</v>
       </c>
       <c r="I30" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J30" s="41" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K30" s="46"/>
       <c r="L30" s="44"/>
-      <c r="M30" s="47"/>
+      <c r="M30" s="49"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A31" s="16">
@@ -2000,7 +1997,7 @@
       </c>
       <c r="E31" s="18"/>
       <c r="F31" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G31" s="16" t="s">
         <v>9</v>
@@ -2009,14 +2006,14 @@
         <v>9</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J31" s="41" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K31" s="46"/>
       <c r="L31" s="44"/>
-      <c r="M31" s="47"/>
+      <c r="M31" s="49"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A32" s="21">
@@ -2031,7 +2028,7 @@
       </c>
       <c r="E32" s="23"/>
       <c r="F32" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G32" s="21" t="s">
         <v>10</v>
@@ -2042,16 +2039,16 @@
       <c r="I32" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="J32" s="52" t="s">
-        <v>121</v>
+      <c r="J32" s="48" t="s">
+        <v>119</v>
       </c>
       <c r="K32" s="46" t="s">
-        <v>113</v>
-      </c>
-      <c r="L32" s="51" t="s">
-        <v>69</v>
-      </c>
-      <c r="M32" s="47"/>
+        <v>111</v>
+      </c>
+      <c r="L32" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="M32" s="49"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A33" s="21">
@@ -2064,7 +2061,7 @@
       </c>
       <c r="E33" s="23"/>
       <c r="F33" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G33" s="21" t="s">
         <v>10</v>
@@ -2075,10 +2072,10 @@
       <c r="I33" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="J33" s="52"/>
+      <c r="J33" s="48"/>
       <c r="K33" s="46"/>
-      <c r="L33" s="51"/>
-      <c r="M33" s="47"/>
+      <c r="L33" s="53"/>
+      <c r="M33" s="49"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A34" s="21">
@@ -2091,7 +2088,7 @@
       </c>
       <c r="E34" s="23"/>
       <c r="F34" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G34" s="21" t="s">
         <v>10</v>
@@ -2103,11 +2100,11 @@
         <v>14</v>
       </c>
       <c r="J34" s="46" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K34" s="46"/>
-      <c r="L34" s="51"/>
-      <c r="M34" s="47"/>
+      <c r="L34" s="53"/>
+      <c r="M34" s="49"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A35" s="21">
@@ -2120,7 +2117,7 @@
       </c>
       <c r="E35" s="23"/>
       <c r="F35" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G35" s="21" t="s">
         <v>10</v>
@@ -2133,8 +2130,8 @@
       </c>
       <c r="J35" s="46"/>
       <c r="K35" s="46"/>
-      <c r="L35" s="51"/>
-      <c r="M35" s="47"/>
+      <c r="L35" s="53"/>
+      <c r="M35" s="49"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A36" s="21">
@@ -2151,7 +2148,7 @@
       </c>
       <c r="E36" s="23"/>
       <c r="F36" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G36" s="21" t="s">
         <v>10</v>
@@ -2164,8 +2161,8 @@
       </c>
       <c r="J36" s="46"/>
       <c r="K36" s="46"/>
-      <c r="L36" s="51"/>
-      <c r="M36" s="47"/>
+      <c r="L36" s="53"/>
+      <c r="M36" s="49"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A37" s="21">
@@ -2178,7 +2175,7 @@
       </c>
       <c r="E37" s="23"/>
       <c r="F37" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G37" s="21" t="s">
         <v>10</v>
@@ -2187,14 +2184,14 @@
         <v>8</v>
       </c>
       <c r="I37" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J37" s="41" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K37" s="46"/>
-      <c r="L37" s="51"/>
-      <c r="M37" s="47"/>
+      <c r="L37" s="53"/>
+      <c r="M37" s="49"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A38" s="21">
@@ -2207,7 +2204,7 @@
       </c>
       <c r="E38" s="23"/>
       <c r="F38" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G38" s="21" t="s">
         <v>10</v>
@@ -2219,11 +2216,11 @@
         <v>16</v>
       </c>
       <c r="J38" s="41" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K38" s="46"/>
-      <c r="L38" s="51"/>
-      <c r="M38" s="47"/>
+      <c r="L38" s="53"/>
+      <c r="M38" s="49"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A39" s="24">
@@ -2241,7 +2238,7 @@
         <v>18</v>
       </c>
       <c r="J39" s="41"/>
-      <c r="M39" s="47"/>
+      <c r="M39" s="49"/>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A40" s="24">
@@ -2261,7 +2258,7 @@
         <v>17</v>
       </c>
       <c r="J40" s="41"/>
-      <c r="M40" s="47"/>
+      <c r="M40" s="49"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A41" s="24">
@@ -2277,7 +2274,7 @@
       <c r="H41" s="26"/>
       <c r="I41" s="25"/>
       <c r="J41" s="41"/>
-      <c r="M41" s="47"/>
+      <c r="M41" s="49"/>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A42" s="24">
@@ -2293,7 +2290,7 @@
       <c r="H42" s="26"/>
       <c r="I42" s="25"/>
       <c r="J42" s="41"/>
-      <c r="M42" s="47"/>
+      <c r="M42" s="49"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A43" s="24">
@@ -2309,7 +2306,7 @@
       <c r="H43" s="26"/>
       <c r="I43" s="25"/>
       <c r="J43" s="41"/>
-      <c r="M43" s="47"/>
+      <c r="M43" s="49"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A44" s="39"/>
@@ -2331,7 +2328,7 @@
       <c r="H45" s="36"/>
       <c r="J45" s="41"/>
       <c r="K45" s="34" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
@@ -2347,13 +2344,13 @@
         <v>8</v>
       </c>
       <c r="J46" s="43" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K46" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="L46" s="37" t="s">
         <v>75</v>
-      </c>
-      <c r="L46" s="37" t="s">
-        <v>77</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
@@ -2369,7 +2366,7 @@
         <v>3</v>
       </c>
       <c r="J47" s="43" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
@@ -2380,22 +2377,12 @@
         <v>9</v>
       </c>
       <c r="J48" s="43" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L48" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="J12:J14"/>
-    <mergeCell ref="J15:J18"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="J34:J36"/>
-    <mergeCell ref="K32:K38"/>
     <mergeCell ref="K2:K9"/>
     <mergeCell ref="K10:K18"/>
     <mergeCell ref="K19:K31"/>
@@ -2404,6 +2391,16 @@
     <mergeCell ref="L2:L9"/>
     <mergeCell ref="L10:L18"/>
     <mergeCell ref="L32:L38"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="J34:J36"/>
+    <mergeCell ref="K32:K38"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="J12:J14"/>
+    <mergeCell ref="J15:J18"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="J24:J25"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>

--- a/docs/Schedule2026.xlsx
+++ b/docs/Schedule2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhouy\Documents\KU2026Seminar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhouy\Documents\4KU\KU2026Seminar\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88604644-7F80-472F-A80F-35FD5F1BDC39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E77F900-E778-4B96-B50E-A917CFD14EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5235" windowWidth="29040" windowHeight="15720" xr2:uid="{F3CF7C89-0ED2-43E9-981B-1B551F77510C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{F3CF7C89-0ED2-43E9-981B-1B551F77510C}"/>
   </bookViews>
   <sheets>
     <sheet name="B" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="100">
   <si>
     <t>Chapter</t>
   </si>
@@ -173,9 +173,6 @@
     <t>Date (time)</t>
   </si>
   <si>
-    <t>Member</t>
-  </si>
-  <si>
     <t>Sufficiency principle</t>
   </si>
   <si>
@@ -183,51 +180,6 @@
   </si>
   <si>
     <t>日本語の参考文献</t>
-  </si>
-  <si>
-    <t>中池紘大</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>橋本大和</t>
-  </si>
-  <si>
-    <t>荒木仁</t>
-  </si>
-  <si>
-    <t>衣川凌太</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>中山想太</t>
-  </si>
-  <si>
-    <t>秋山慶次</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>2491041h@gsuite.kobe-u.ac.jp</t>
-  </si>
-  <si>
-    <t>2401063h@stu.kobe-u.ac.jp</t>
-  </si>
-  <si>
-    <t>2481002h@stu.kobe-u.ac.jp</t>
-  </si>
-  <si>
-    <t>2411014h@stu.kobe-u.ac.jp</t>
-  </si>
-  <si>
-    <t>2251021h@stu.kobe-u.ac.jp</t>
   </si>
   <si>
     <t>前期：多変量解析（Linear regression, logistic regression）、計算機科学入門（R、Python）</t>
@@ -246,18 +198,6 @@
     <t>Epidemiological studies</t>
   </si>
   <si>
-    <t>郑旺（ZHENG Wang）</t>
-  </si>
-  <si>
-    <t>2461034h@stu.kobe-u.ac.jp</t>
-  </si>
-  <si>
-    <t>envan.zheng@gmail.com</t>
-  </si>
-  <si>
-    <t>Speaker</t>
-  </si>
-  <si>
     <t>https://pages.stat.wisc.edu/~shao/stat610/Casella_Berger_Statistical_Inference.pdf</t>
   </si>
   <si>
@@ -321,15 +261,6 @@
     <t>simulation、ベイズ法に関連する</t>
   </si>
   <si>
-    <t>ZHOU 周</t>
-  </si>
-  <si>
-    <t>zhouy@people.kobe-u.ac.jp</t>
-  </si>
-  <si>
-    <t>5*7回</t>
-  </si>
-  <si>
     <t>科目</t>
   </si>
   <si>
@@ -403,9 +334,6 @@
   </si>
   <si>
     <t>PSの利用（Real word data）、交絡因子</t>
-  </si>
-  <si>
-    <t>268de05d@stu.kobe-u.ac.jp</t>
   </si>
   <si>
     <t>Hierachical model, EM algorithm</t>
@@ -669,26 +597,26 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1061,9 +989,7 @@
       <c r="E1" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="29" t="s">
-        <v>72</v>
-      </c>
+      <c r="F1" s="29"/>
       <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1074,23 +1000,18 @@
         <v>4</v>
       </c>
       <c r="J1" s="41" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="K1" s="34" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="L1" s="34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M1" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="O1" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>50</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="O1" s="11"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A2" s="6">
@@ -1106,9 +1027,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="8"/>
-      <c r="F2" s="3" t="s">
-        <v>49</v>
-      </c>
+      <c r="F2" s="3"/>
       <c r="G2" s="9" t="s">
         <v>8</v>
       </c>
@@ -1116,29 +1035,23 @@
         <v>19</v>
       </c>
       <c r="I2" s="30" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="J2" s="42" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="K2" s="46" t="s">
-        <v>110</v>
-      </c>
-      <c r="L2" s="50" t="s">
-        <v>66</v>
-      </c>
-      <c r="M2" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>60</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="L2" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="M2" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="3"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A3" s="6">
@@ -1150,9 +1063,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="8"/>
-      <c r="F3" s="3" t="s">
-        <v>51</v>
-      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="9" t="s">
         <v>8</v>
       </c>
@@ -1160,23 +1071,17 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I3" s="30" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="J3" s="42" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="K3" s="46"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="49"/>
-      <c r="N3" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>61</v>
-      </c>
+      <c r="L3" s="49"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="3"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A4" s="6">
@@ -1188,9 +1093,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="8"/>
-      <c r="F4" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="F4" s="3"/>
       <c r="G4" s="9" t="s">
         <v>8</v>
       </c>
@@ -1201,20 +1104,14 @@
         <v>23</v>
       </c>
       <c r="J4" s="42" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="K4" s="46"/>
-      <c r="L4" s="51"/>
-      <c r="M4" s="49"/>
-      <c r="N4" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="O4" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>70</v>
-      </c>
+      <c r="L4" s="49"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="3"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A5" s="6">
@@ -1226,9 +1123,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="8"/>
-      <c r="F5" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="F5" s="3"/>
       <c r="G5" s="9" t="s">
         <v>8</v>
       </c>
@@ -1239,20 +1134,14 @@
         <v>24</v>
       </c>
       <c r="J5" s="42" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="K5" s="46"/>
-      <c r="L5" s="51"/>
-      <c r="M5" s="49"/>
-      <c r="N5" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>62</v>
-      </c>
+      <c r="L5" s="49"/>
+      <c r="M5" s="47"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="3"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A6" s="6">
@@ -1266,9 +1155,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="8"/>
-      <c r="F6" s="3" t="s">
-        <v>57</v>
-      </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="9" t="s">
         <v>8</v>
       </c>
@@ -1276,23 +1163,17 @@
         <v>38</v>
       </c>
       <c r="I6" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="J6" s="47" t="s">
-        <v>99</v>
+        <v>45</v>
+      </c>
+      <c r="J6" s="53" t="s">
+        <v>76</v>
       </c>
       <c r="K6" s="46"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="49"/>
-      <c r="N6" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="O6" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>59</v>
-      </c>
+      <c r="L6" s="49"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="3"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A7" s="6">
@@ -1304,9 +1185,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="8"/>
-      <c r="F7" s="3" t="s">
-        <v>49</v>
-      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="9" t="s">
         <v>8</v>
       </c>
@@ -1314,15 +1193,13 @@
         <v>39</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="J7" s="47"/>
+        <v>45</v>
+      </c>
+      <c r="J7" s="53"/>
       <c r="K7" s="46"/>
-      <c r="L7" s="51"/>
-      <c r="M7" s="49"/>
-      <c r="O7" s="11" t="s">
-        <v>96</v>
-      </c>
+      <c r="L7" s="49"/>
+      <c r="M7" s="47"/>
+      <c r="O7" s="11"/>
       <c r="P7" s="3"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.4">
@@ -1335,9 +1212,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="8"/>
-      <c r="F8" s="3" t="s">
-        <v>51</v>
-      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="9" t="s">
         <v>8</v>
       </c>
@@ -1348,11 +1223,11 @@
         <v>26</v>
       </c>
       <c r="J8" s="42" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="K8" s="46"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="49"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="47"/>
       <c r="P8" s="3"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.4">
@@ -1365,9 +1240,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="8"/>
-      <c r="F9" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="F9" s="3"/>
       <c r="G9" s="9" t="s">
         <v>8</v>
       </c>
@@ -1375,23 +1248,15 @@
         <v>20</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="J9" s="42" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="K9" s="46"/>
-      <c r="L9" s="51"/>
-      <c r="M9" s="49"/>
-      <c r="N9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="L9" s="49"/>
+      <c r="M9" s="47"/>
+      <c r="P9" s="3"/>
       <c r="Q9" s="27"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.4">
@@ -1406,9 +1271,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="14"/>
-      <c r="F10" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="F10" s="3"/>
       <c r="G10" s="12" t="s">
         <v>3</v>
       </c>
@@ -1419,24 +1282,16 @@
         <v>22</v>
       </c>
       <c r="J10" s="46" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="K10" s="46" t="s">
-        <v>116</v>
-      </c>
-      <c r="L10" s="52" t="s">
-        <v>47</v>
-      </c>
-      <c r="M10" s="49"/>
-      <c r="N10" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>71</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="L10" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="M10" s="47"/>
+      <c r="P10" s="3"/>
       <c r="Q10" s="27"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.4">
@@ -1449,9 +1304,7 @@
         <v>2</v>
       </c>
       <c r="E11" s="14"/>
-      <c r="F11" s="3" t="s">
-        <v>57</v>
-      </c>
+      <c r="F11" s="3"/>
       <c r="G11" s="12" t="s">
         <v>3</v>
       </c>
@@ -1463,11 +1316,8 @@
       </c>
       <c r="J11" s="46"/>
       <c r="K11" s="46"/>
-      <c r="L11" s="52"/>
-      <c r="M11" s="49"/>
-      <c r="P11" s="4" t="s">
-        <v>122</v>
-      </c>
+      <c r="L11" s="50"/>
+      <c r="M11" s="47"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A12" s="12">
@@ -1479,9 +1329,7 @@
         <v>3</v>
       </c>
       <c r="E12" s="14"/>
-      <c r="F12" s="3" t="s">
-        <v>49</v>
-      </c>
+      <c r="F12" s="3"/>
       <c r="G12" s="12" t="s">
         <v>3</v>
       </c>
@@ -1489,20 +1337,16 @@
         <v>30</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="J12" s="46" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="K12" s="46"/>
-      <c r="L12" s="52"/>
-      <c r="M12" s="49"/>
-      <c r="O12" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>95</v>
-      </c>
+      <c r="L12" s="50"/>
+      <c r="M12" s="47"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="3"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A13" s="12">
@@ -1514,9 +1358,7 @@
         <v>4</v>
       </c>
       <c r="E13" s="14"/>
-      <c r="F13" s="3" t="s">
-        <v>51</v>
-      </c>
+      <c r="F13" s="3"/>
       <c r="G13" s="12" t="s">
         <v>3</v>
       </c>
@@ -1528,8 +1370,8 @@
       </c>
       <c r="J13" s="46"/>
       <c r="K13" s="46"/>
-      <c r="L13" s="52"/>
-      <c r="M13" s="49"/>
+      <c r="L13" s="50"/>
+      <c r="M13" s="47"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A14" s="12">
@@ -1543,9 +1385,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="14"/>
-      <c r="F14" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="F14" s="3"/>
       <c r="G14" s="12" t="s">
         <v>3</v>
       </c>
@@ -1557,8 +1397,8 @@
       </c>
       <c r="J14" s="46"/>
       <c r="K14" s="46"/>
-      <c r="L14" s="52"/>
-      <c r="M14" s="49"/>
+      <c r="L14" s="50"/>
+      <c r="M14" s="47"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A15" s="12">
@@ -1570,9 +1410,7 @@
         <v>2</v>
       </c>
       <c r="E15" s="14"/>
-      <c r="F15" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="F15" s="3"/>
       <c r="G15" s="12" t="s">
         <v>3</v>
       </c>
@@ -1583,11 +1421,11 @@
         <v>7</v>
       </c>
       <c r="J15" s="46" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="K15" s="46"/>
-      <c r="L15" s="52"/>
-      <c r="M15" s="49"/>
+      <c r="L15" s="50"/>
+      <c r="M15" s="47"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A16" s="12">
@@ -1599,9 +1437,7 @@
         <v>3</v>
       </c>
       <c r="E16" s="14"/>
-      <c r="F16" s="3" t="s">
-        <v>57</v>
-      </c>
+      <c r="F16" s="3"/>
       <c r="G16" s="12" t="s">
         <v>3</v>
       </c>
@@ -1613,8 +1449,8 @@
       </c>
       <c r="J16" s="46"/>
       <c r="K16" s="46"/>
-      <c r="L16" s="52"/>
-      <c r="M16" s="49"/>
+      <c r="L16" s="50"/>
+      <c r="M16" s="47"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A17" s="12">
@@ -1626,9 +1462,7 @@
         <v>4</v>
       </c>
       <c r="E17" s="14"/>
-      <c r="F17" s="3" t="s">
-        <v>49</v>
-      </c>
+      <c r="F17" s="3"/>
       <c r="G17" s="12" t="s">
         <v>3</v>
       </c>
@@ -1640,8 +1474,8 @@
       </c>
       <c r="J17" s="46"/>
       <c r="K17" s="46"/>
-      <c r="L17" s="52"/>
-      <c r="M17" s="49"/>
+      <c r="L17" s="50"/>
+      <c r="M17" s="47"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A18" s="12">
@@ -1655,9 +1489,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="14"/>
-      <c r="F18" s="3" t="s">
-        <v>51</v>
-      </c>
+      <c r="F18" s="3"/>
       <c r="G18" s="12" t="s">
         <v>3</v>
       </c>
@@ -1669,8 +1501,8 @@
       </c>
       <c r="J18" s="46"/>
       <c r="K18" s="46"/>
-      <c r="L18" s="52"/>
-      <c r="M18" s="49"/>
+      <c r="L18" s="50"/>
+      <c r="M18" s="47"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A19" s="16">
@@ -1682,25 +1514,23 @@
         <v>2</v>
       </c>
       <c r="E19" s="18"/>
-      <c r="F19" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="F19" s="3"/>
       <c r="G19" s="16" t="s">
         <v>9</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="I19" s="17" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="J19" s="41" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="K19" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="M19" s="49"/>
+        <v>94</v>
+      </c>
+      <c r="M19" s="47"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A20" s="16">
@@ -1712,23 +1542,21 @@
         <v>3</v>
       </c>
       <c r="E20" s="18"/>
-      <c r="F20" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="F20" s="3"/>
       <c r="G20" s="16" t="s">
         <v>9</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="J20" s="41" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="K20" s="46"/>
-      <c r="M20" s="49"/>
+      <c r="M20" s="47"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A21" s="16">
@@ -1740,20 +1568,18 @@
         <v>4</v>
       </c>
       <c r="E21" s="18"/>
-      <c r="F21" s="3" t="s">
-        <v>57</v>
-      </c>
+      <c r="F21" s="3"/>
       <c r="G21" s="16" t="s">
         <v>9</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="J21" s="41" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="K21" s="46"/>
     </row>
@@ -1801,24 +1627,22 @@
         <v>1</v>
       </c>
       <c r="E24" s="18"/>
-      <c r="F24" s="3" t="s">
-        <v>49</v>
-      </c>
+      <c r="F24" s="3"/>
       <c r="G24" s="16" t="s">
         <v>9</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="J24" s="46" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="K24" s="46"/>
-      <c r="M24" s="49" t="s">
-        <v>65</v>
+      <c r="M24" s="47" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.4">
@@ -1831,21 +1655,19 @@
         <v>2</v>
       </c>
       <c r="E25" s="18"/>
-      <c r="F25" s="3" t="s">
-        <v>51</v>
-      </c>
+      <c r="F25" s="3"/>
       <c r="G25" s="16" t="s">
         <v>9</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="I25" s="17" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="J25" s="46"/>
       <c r="K25" s="46"/>
-      <c r="M25" s="49"/>
+      <c r="M25" s="47"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A26" s="16">
@@ -1857,9 +1679,7 @@
         <v>3</v>
       </c>
       <c r="E26" s="18"/>
-      <c r="F26" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="F26" s="3"/>
       <c r="G26" s="16" t="s">
         <v>9</v>
       </c>
@@ -1870,10 +1690,10 @@
         <v>40</v>
       </c>
       <c r="J26" s="46" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="K26" s="46"/>
-      <c r="M26" s="49"/>
+      <c r="M26" s="47"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A27" s="16">
@@ -1885,9 +1705,7 @@
         <v>4</v>
       </c>
       <c r="E27" s="18"/>
-      <c r="F27" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="F27" s="3"/>
       <c r="G27" s="16" t="s">
         <v>9</v>
       </c>
@@ -1899,7 +1717,7 @@
       </c>
       <c r="J27" s="46"/>
       <c r="K27" s="46"/>
-      <c r="M27" s="49"/>
+      <c r="M27" s="47"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A28" s="16">
@@ -1913,9 +1731,7 @@
         <v>1</v>
       </c>
       <c r="E28" s="18"/>
-      <c r="F28" s="3" t="s">
-        <v>57</v>
-      </c>
+      <c r="F28" s="3"/>
       <c r="G28" s="16" t="s">
         <v>9</v>
       </c>
@@ -1926,10 +1742,10 @@
         <v>41</v>
       </c>
       <c r="J28" s="46" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="K28" s="46"/>
-      <c r="M28" s="49"/>
+      <c r="M28" s="47"/>
     </row>
     <row r="29" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="16">
@@ -1941,9 +1757,7 @@
         <v>2</v>
       </c>
       <c r="E29" s="18"/>
-      <c r="F29" s="3" t="s">
-        <v>49</v>
-      </c>
+      <c r="F29" s="3"/>
       <c r="G29" s="16" t="s">
         <v>9</v>
       </c>
@@ -1955,7 +1769,7 @@
       </c>
       <c r="J29" s="46"/>
       <c r="K29" s="46"/>
-      <c r="M29" s="49"/>
+      <c r="M29" s="47"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A30" s="16">
@@ -1967,9 +1781,7 @@
         <v>3</v>
       </c>
       <c r="E30" s="18"/>
-      <c r="F30" s="3" t="s">
-        <v>51</v>
-      </c>
+      <c r="F30" s="3"/>
       <c r="G30" s="16" t="s">
         <v>9</v>
       </c>
@@ -1980,11 +1792,11 @@
         <v>42</v>
       </c>
       <c r="J30" s="41" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="K30" s="46"/>
       <c r="L30" s="44"/>
-      <c r="M30" s="49"/>
+      <c r="M30" s="47"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A31" s="16">
@@ -1996,9 +1808,7 @@
         <v>4</v>
       </c>
       <c r="E31" s="18"/>
-      <c r="F31" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="F31" s="3"/>
       <c r="G31" s="16" t="s">
         <v>9</v>
       </c>
@@ -2006,14 +1816,14 @@
         <v>9</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="J31" s="41" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="K31" s="46"/>
       <c r="L31" s="44"/>
-      <c r="M31" s="49"/>
+      <c r="M31" s="47"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A32" s="21">
@@ -2027,9 +1837,7 @@
         <v>1</v>
       </c>
       <c r="E32" s="23"/>
-      <c r="F32" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="F32" s="3"/>
       <c r="G32" s="21" t="s">
         <v>10</v>
       </c>
@@ -2039,16 +1847,16 @@
       <c r="I32" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="J32" s="48" t="s">
-        <v>119</v>
+      <c r="J32" s="52" t="s">
+        <v>96</v>
       </c>
       <c r="K32" s="46" t="s">
-        <v>111</v>
-      </c>
-      <c r="L32" s="53" t="s">
-        <v>67</v>
-      </c>
-      <c r="M32" s="49"/>
+        <v>88</v>
+      </c>
+      <c r="L32" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="M32" s="47"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A33" s="21">
@@ -2060,9 +1868,7 @@
         <v>2</v>
       </c>
       <c r="E33" s="23"/>
-      <c r="F33" s="3" t="s">
-        <v>57</v>
-      </c>
+      <c r="F33" s="3"/>
       <c r="G33" s="21" t="s">
         <v>10</v>
       </c>
@@ -2072,10 +1878,10 @@
       <c r="I33" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="J33" s="48"/>
+      <c r="J33" s="52"/>
       <c r="K33" s="46"/>
-      <c r="L33" s="53"/>
-      <c r="M33" s="49"/>
+      <c r="L33" s="51"/>
+      <c r="M33" s="47"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A34" s="21">
@@ -2087,9 +1893,7 @@
         <v>3</v>
       </c>
       <c r="E34" s="23"/>
-      <c r="F34" s="3" t="s">
-        <v>49</v>
-      </c>
+      <c r="F34" s="3"/>
       <c r="G34" s="21" t="s">
         <v>10</v>
       </c>
@@ -2100,11 +1904,11 @@
         <v>14</v>
       </c>
       <c r="J34" s="46" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="K34" s="46"/>
-      <c r="L34" s="53"/>
-      <c r="M34" s="49"/>
+      <c r="L34" s="51"/>
+      <c r="M34" s="47"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A35" s="21">
@@ -2116,9 +1920,7 @@
         <v>4</v>
       </c>
       <c r="E35" s="23"/>
-      <c r="F35" s="3" t="s">
-        <v>51</v>
-      </c>
+      <c r="F35" s="3"/>
       <c r="G35" s="21" t="s">
         <v>10</v>
       </c>
@@ -2130,8 +1932,8 @@
       </c>
       <c r="J35" s="46"/>
       <c r="K35" s="46"/>
-      <c r="L35" s="53"/>
-      <c r="M35" s="49"/>
+      <c r="L35" s="51"/>
+      <c r="M35" s="47"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A36" s="21">
@@ -2147,9 +1949,7 @@
         <v>1</v>
       </c>
       <c r="E36" s="23"/>
-      <c r="F36" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="F36" s="3"/>
       <c r="G36" s="21" t="s">
         <v>10</v>
       </c>
@@ -2161,8 +1961,8 @@
       </c>
       <c r="J36" s="46"/>
       <c r="K36" s="46"/>
-      <c r="L36" s="53"/>
-      <c r="M36" s="49"/>
+      <c r="L36" s="51"/>
+      <c r="M36" s="47"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A37" s="21">
@@ -2174,9 +1974,7 @@
         <v>2</v>
       </c>
       <c r="E37" s="23"/>
-      <c r="F37" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="21" t="s">
         <v>10</v>
       </c>
@@ -2187,11 +1985,11 @@
         <v>43</v>
       </c>
       <c r="J37" s="41" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="K37" s="46"/>
-      <c r="L37" s="53"/>
-      <c r="M37" s="49"/>
+      <c r="L37" s="51"/>
+      <c r="M37" s="47"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A38" s="21">
@@ -2203,9 +2001,7 @@
         <v>3</v>
       </c>
       <c r="E38" s="23"/>
-      <c r="F38" s="3" t="s">
-        <v>57</v>
-      </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="21" t="s">
         <v>10</v>
       </c>
@@ -2216,11 +2012,11 @@
         <v>16</v>
       </c>
       <c r="J38" s="41" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="K38" s="46"/>
-      <c r="L38" s="53"/>
-      <c r="M38" s="49"/>
+      <c r="L38" s="51"/>
+      <c r="M38" s="47"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A39" s="24">
@@ -2238,7 +2034,7 @@
         <v>18</v>
       </c>
       <c r="J39" s="41"/>
-      <c r="M39" s="49"/>
+      <c r="M39" s="47"/>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A40" s="24">
@@ -2258,7 +2054,7 @@
         <v>17</v>
       </c>
       <c r="J40" s="41"/>
-      <c r="M40" s="49"/>
+      <c r="M40" s="47"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A41" s="24">
@@ -2274,7 +2070,7 @@
       <c r="H41" s="26"/>
       <c r="I41" s="25"/>
       <c r="J41" s="41"/>
-      <c r="M41" s="49"/>
+      <c r="M41" s="47"/>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A42" s="24">
@@ -2290,7 +2086,7 @@
       <c r="H42" s="26"/>
       <c r="I42" s="25"/>
       <c r="J42" s="41"/>
-      <c r="M42" s="49"/>
+      <c r="M42" s="47"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A43" s="24">
@@ -2306,7 +2102,7 @@
       <c r="H43" s="26"/>
       <c r="I43" s="25"/>
       <c r="J43" s="41"/>
-      <c r="M43" s="49"/>
+      <c r="M43" s="47"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A44" s="39"/>
@@ -2328,7 +2124,7 @@
       <c r="H45" s="36"/>
       <c r="J45" s="41"/>
       <c r="K45" s="34" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
@@ -2344,13 +2140,13 @@
         <v>8</v>
       </c>
       <c r="J46" s="43" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="K46" s="35" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="L46" s="37" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
@@ -2366,7 +2162,7 @@
         <v>3</v>
       </c>
       <c r="J47" s="43" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
@@ -2377,12 +2173,22 @@
         <v>9</v>
       </c>
       <c r="J48" s="43" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="L48" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="J12:J14"/>
+    <mergeCell ref="J15:J18"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="J34:J36"/>
+    <mergeCell ref="K32:K38"/>
     <mergeCell ref="K2:K9"/>
     <mergeCell ref="K10:K18"/>
     <mergeCell ref="K19:K31"/>
@@ -2391,37 +2197,19 @@
     <mergeCell ref="L2:L9"/>
     <mergeCell ref="L10:L18"/>
     <mergeCell ref="L32:L38"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="J34:J36"/>
-    <mergeCell ref="K32:K38"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="J12:J14"/>
-    <mergeCell ref="J15:J18"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="J24:J25"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="L2" r:id="rId1" display="https://elib.maruzen.co.jp/elib/html/BookDetail/Id/3000105174" xr:uid="{364EEF0A-19CD-479A-A947-760F07C8154B}"/>
     <hyperlink ref="L10" r:id="rId2" xr:uid="{C3C70617-B872-4D47-9431-E32204BD231C}"/>
-    <hyperlink ref="P6" r:id="rId3" xr:uid="{54DC86B5-FCC6-44F9-BA2E-D248ECA94439}"/>
-    <hyperlink ref="P2" r:id="rId4" xr:uid="{9221181A-88E4-42FB-B54B-614904183425}"/>
-    <hyperlink ref="P3" r:id="rId5" xr:uid="{5750C2F7-DBE5-46EC-A4EC-74E1A35A1760}"/>
-    <hyperlink ref="P5" r:id="rId6" xr:uid="{293B3A7A-F82A-45E8-A411-4064A7EC316D}"/>
-    <hyperlink ref="P9" r:id="rId7" xr:uid="{A9A21EDC-6A33-49A3-BD30-82D46AD8EFE9}"/>
-    <hyperlink ref="L32" r:id="rId8" xr:uid="{D7DC9A32-1E31-48DB-959D-1D80765B15C1}"/>
-    <hyperlink ref="P4" r:id="rId9" xr:uid="{1A8C861F-E95A-464F-8634-EFD0080595D5}"/>
-    <hyperlink ref="P10" r:id="rId10" xr:uid="{8BACA04F-6EFE-47A7-AA3F-7F493B4AB06F}"/>
-    <hyperlink ref="K46" r:id="rId11" xr:uid="{5F48F631-EFC0-4ABA-B165-8D97636C56CB}"/>
-    <hyperlink ref="J48" r:id="rId12" xr:uid="{EFAFC658-877D-463E-B637-CA7188024480}"/>
-    <hyperlink ref="L46" r:id="rId13" xr:uid="{480389A4-D45F-4E43-904C-C3F7C604E01E}"/>
-    <hyperlink ref="J46" r:id="rId14" xr:uid="{1385B894-421E-4212-8D5C-4AB875764389}"/>
-    <hyperlink ref="J47" r:id="rId15" xr:uid="{6D2D26B4-CD95-49A6-BBFE-160A8F5360A4}"/>
-    <hyperlink ref="P12" r:id="rId16" xr:uid="{040E38E8-2DE0-42D4-86C8-CBA02145A1C0}"/>
+    <hyperlink ref="L32" r:id="rId3" xr:uid="{D7DC9A32-1E31-48DB-959D-1D80765B15C1}"/>
+    <hyperlink ref="K46" r:id="rId4" xr:uid="{5F48F631-EFC0-4ABA-B165-8D97636C56CB}"/>
+    <hyperlink ref="J48" r:id="rId5" xr:uid="{EFAFC658-877D-463E-B637-CA7188024480}"/>
+    <hyperlink ref="L46" r:id="rId6" xr:uid="{480389A4-D45F-4E43-904C-C3F7C604E01E}"/>
+    <hyperlink ref="J46" r:id="rId7" xr:uid="{1385B894-421E-4212-8D5C-4AB875764389}"/>
+    <hyperlink ref="J47" r:id="rId8" xr:uid="{6D2D26B4-CD95-49A6-BBFE-160A8F5360A4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId17"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>
--- a/docs/Schedule2026.xlsx
+++ b/docs/Schedule2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhouy\Documents\4KU\KU2026Seminar\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E77F900-E778-4B96-B50E-A917CFD14EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6622BB6-EBB7-4F4A-9B38-A83363540353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{F3CF7C89-0ED2-43E9-981B-1B551F77510C}"/>
   </bookViews>
@@ -182,12 +182,6 @@
     <t>日本語の参考文献</t>
   </si>
   <si>
-    <t>前期：多変量解析（Linear regression, logistic regression）、計算機科学入門（R、Python）</t>
-  </si>
-  <si>
-    <t>後期：数理モデルプログラミング（C）</t>
-  </si>
-  <si>
     <t>https://elib.maruzen.co.jp/elib/html/BookDetail/Id/3000105174　
 https://elib.maruzen.co.jp/elib/html/BookDetail/Id/3000050917</t>
   </si>
@@ -337,6 +331,12 @@
   </si>
   <si>
     <t>Hierachical model, EM algorithm</t>
+  </si>
+  <si>
+    <t>後期：数理モデル</t>
+  </si>
+  <si>
+    <t>前期：多変量解析（Linear regression, logistic regression）</t>
   </si>
 </sst>
 </file>
@@ -1000,16 +1000,16 @@
         <v>4</v>
       </c>
       <c r="J1" s="41" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K1" s="34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L1" s="34" t="s">
         <v>47</v>
       </c>
       <c r="M1" s="34" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O1" s="11"/>
     </row>
@@ -1035,19 +1035,19 @@
         <v>19</v>
       </c>
       <c r="I2" s="30" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J2" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K2" s="46" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="L2" s="48" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M2" s="47" t="s">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="N2" s="11"/>
       <c r="O2" s="11"/>
@@ -1071,10 +1071,10 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I3" s="30" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J3" s="42" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K3" s="46"/>
       <c r="L3" s="49"/>
@@ -1104,7 +1104,7 @@
         <v>23</v>
       </c>
       <c r="J4" s="42" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K4" s="46"/>
       <c r="L4" s="49"/>
@@ -1134,7 +1134,7 @@
         <v>24</v>
       </c>
       <c r="J5" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K5" s="46"/>
       <c r="L5" s="49"/>
@@ -1166,7 +1166,7 @@
         <v>45</v>
       </c>
       <c r="J6" s="53" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K6" s="46"/>
       <c r="L6" s="49"/>
@@ -1223,7 +1223,7 @@
         <v>26</v>
       </c>
       <c r="J8" s="42" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K8" s="46"/>
       <c r="L8" s="49"/>
@@ -1248,10 +1248,10 @@
         <v>20</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J9" s="42" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K9" s="46"/>
       <c r="L9" s="49"/>
@@ -1282,10 +1282,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="46" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K10" s="46" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L10" s="50" t="s">
         <v>46</v>
@@ -1337,10 +1337,10 @@
         <v>30</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J12" s="46" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K12" s="46"/>
       <c r="L12" s="50"/>
@@ -1421,7 +1421,7 @@
         <v>7</v>
       </c>
       <c r="J15" s="46" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K15" s="46"/>
       <c r="L15" s="50"/>
@@ -1519,16 +1519,16 @@
         <v>9</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I19" s="17" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J19" s="41" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K19" s="46" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M19" s="47"/>
     </row>
@@ -1547,13 +1547,13 @@
         <v>9</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J20" s="41" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K20" s="46"/>
       <c r="M20" s="47"/>
@@ -1573,13 +1573,13 @@
         <v>9</v>
       </c>
       <c r="H21" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="I21" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="J21" s="41" t="s">
         <v>64</v>
-      </c>
-      <c r="I21" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="J21" s="41" t="s">
-        <v>66</v>
       </c>
       <c r="K21" s="46"/>
     </row>
@@ -1632,17 +1632,17 @@
         <v>9</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J24" s="46" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K24" s="46"/>
       <c r="M24" s="47" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.4">
@@ -1660,10 +1660,10 @@
         <v>9</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I25" s="17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J25" s="46"/>
       <c r="K25" s="46"/>
@@ -1690,7 +1690,7 @@
         <v>40</v>
       </c>
       <c r="J26" s="46" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K26" s="46"/>
       <c r="M26" s="47"/>
@@ -1742,7 +1742,7 @@
         <v>41</v>
       </c>
       <c r="J28" s="46" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K28" s="46"/>
       <c r="M28" s="47"/>
@@ -1792,7 +1792,7 @@
         <v>42</v>
       </c>
       <c r="J30" s="41" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K30" s="46"/>
       <c r="L30" s="44"/>
@@ -1816,10 +1816,10 @@
         <v>9</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J31" s="41" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K31" s="46"/>
       <c r="L31" s="44"/>
@@ -1848,13 +1848,13 @@
         <v>11</v>
       </c>
       <c r="J32" s="52" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K32" s="46" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L32" s="51" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M32" s="47"/>
     </row>
@@ -1904,7 +1904,7 @@
         <v>14</v>
       </c>
       <c r="J34" s="46" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K34" s="46"/>
       <c r="L34" s="51"/>
@@ -1985,7 +1985,7 @@
         <v>43</v>
       </c>
       <c r="J37" s="41" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K37" s="46"/>
       <c r="L37" s="51"/>
@@ -2012,7 +2012,7 @@
         <v>16</v>
       </c>
       <c r="J38" s="41" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K38" s="46"/>
       <c r="L38" s="51"/>
@@ -2124,7 +2124,7 @@
       <c r="H45" s="36"/>
       <c r="J45" s="41"/>
       <c r="K45" s="34" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
@@ -2140,13 +2140,13 @@
         <v>8</v>
       </c>
       <c r="J46" s="43" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K46" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="L46" s="37" t="s">
         <v>53</v>
-      </c>
-      <c r="L46" s="37" t="s">
-        <v>55</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
@@ -2162,7 +2162,7 @@
         <v>3</v>
       </c>
       <c r="J47" s="43" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
@@ -2173,7 +2173,7 @@
         <v>9</v>
       </c>
       <c r="J48" s="43" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L48" s="2"/>
     </row>

--- a/docs/Schedule2026.xlsx
+++ b/docs/Schedule2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhouy\Documents\4KU\KU2026Seminar\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhouy\Documents\4KU\KU2026Seminar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6622BB6-EBB7-4F4A-9B38-A83363540353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82AE5616-19FB-48C2-A8CB-004E6665A8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{F3CF7C89-0ED2-43E9-981B-1B551F77510C}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12645" xr2:uid="{F3CF7C89-0ED2-43E9-981B-1B551F77510C}"/>
   </bookViews>
   <sheets>
     <sheet name="B" sheetId="2" r:id="rId1"/>
@@ -182,6 +182,12 @@
     <t>日本語の参考文献</t>
   </si>
   <si>
+    <t>前期：多変量解析（Linear regression, logistic regression）、計算機科学入門（R、Python）</t>
+  </si>
+  <si>
+    <t>後期：数理モデルプログラミング（C）</t>
+  </si>
+  <si>
     <t>https://elib.maruzen.co.jp/elib/html/BookDetail/Id/3000105174　
 https://elib.maruzen.co.jp/elib/html/BookDetail/Id/3000050917</t>
   </si>
@@ -331,12 +337,6 @@
   </si>
   <si>
     <t>Hierachical model, EM algorithm</t>
-  </si>
-  <si>
-    <t>後期：数理モデル</t>
-  </si>
-  <si>
-    <t>前期：多変量解析（Linear regression, logistic regression）</t>
   </si>
 </sst>
 </file>
@@ -597,6 +597,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -611,12 +617,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -953,7 +953,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F8C7450-5724-4580-A29D-E4706F6B038E}">
-  <dimension ref="A1:Q48"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.375" style="5" bestFit="1" customWidth="1"/>
@@ -969,13 +969,12 @@
     <col min="11" max="11" width="23.25" style="2" customWidth="1"/>
     <col min="12" max="12" width="32.375" style="5" customWidth="1"/>
     <col min="13" max="13" width="16.75" style="2" customWidth="1"/>
-    <col min="14" max="14" width="4.5" style="3" customWidth="1"/>
-    <col min="15" max="15" width="20.5" style="3" customWidth="1"/>
-    <col min="16" max="16" width="32.25" style="4" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="5"/>
+    <col min="14" max="14" width="20.5" style="3" customWidth="1"/>
+    <col min="15" max="15" width="32.25" style="4" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -1000,20 +999,19 @@
         <v>4</v>
       </c>
       <c r="J1" s="41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K1" s="34" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L1" s="34" t="s">
         <v>47</v>
       </c>
       <c r="M1" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="O1" s="11"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -1035,25 +1033,22 @@
         <v>19</v>
       </c>
       <c r="I2" s="30" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J2" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="K2" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="K2" s="46" t="s">
-        <v>85</v>
-      </c>
-      <c r="L2" s="48" t="s">
+      <c r="L2" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="M2" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="M2" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="3"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -1071,19 +1066,16 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I3" s="30" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J3" s="42" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K3" s="46"/>
-      <c r="L3" s="49"/>
-      <c r="M3" s="47"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="3"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="L3" s="51"/>
+      <c r="M3" s="49"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -1104,16 +1096,13 @@
         <v>23</v>
       </c>
       <c r="J4" s="42" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K4" s="46"/>
-      <c r="L4" s="49"/>
-      <c r="M4" s="47"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="3"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="L4" s="51"/>
+      <c r="M4" s="49"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -1134,16 +1123,13 @@
         <v>24</v>
       </c>
       <c r="J5" s="42" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K5" s="46"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="47"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="3"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="L5" s="51"/>
+      <c r="M5" s="49"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -1165,17 +1151,14 @@
       <c r="I6" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="J6" s="53" t="s">
-        <v>74</v>
+      <c r="J6" s="47" t="s">
+        <v>76</v>
       </c>
       <c r="K6" s="46"/>
-      <c r="L6" s="49"/>
-      <c r="M6" s="47"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="3"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="L6" s="51"/>
+      <c r="M6" s="49"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -1195,14 +1178,12 @@
       <c r="I7" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="J7" s="53"/>
+      <c r="J7" s="47"/>
       <c r="K7" s="46"/>
-      <c r="L7" s="49"/>
-      <c r="M7" s="47"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="3"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="L7" s="51"/>
+      <c r="M7" s="49"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8" s="6">
         <v>7</v>
       </c>
@@ -1223,14 +1204,13 @@
         <v>26</v>
       </c>
       <c r="J8" s="42" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K8" s="46"/>
-      <c r="L8" s="49"/>
-      <c r="M8" s="47"/>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="L8" s="51"/>
+      <c r="M8" s="49"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -1248,18 +1228,16 @@
         <v>20</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J9" s="42" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K9" s="46"/>
-      <c r="L9" s="49"/>
-      <c r="M9" s="47"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="27"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="L9" s="51"/>
+      <c r="M9" s="49"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A10" s="12">
         <v>9</v>
       </c>
@@ -1282,19 +1260,20 @@
         <v>22</v>
       </c>
       <c r="J10" s="46" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K10" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="L10" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="L10" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="M10" s="47"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="27"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="M10" s="49"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="19"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A11" s="12">
         <v>10</v>
       </c>
@@ -1316,10 +1295,13 @@
       </c>
       <c r="J11" s="46"/>
       <c r="K11" s="46"/>
-      <c r="L11" s="50"/>
-      <c r="M11" s="47"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="L11" s="52"/>
+      <c r="M11" s="49"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="19"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A12" s="12">
         <v>11</v>
       </c>
@@ -1337,18 +1319,16 @@
         <v>30</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J12" s="46" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K12" s="46"/>
-      <c r="L12" s="50"/>
-      <c r="M12" s="47"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="L12" s="52"/>
+      <c r="M12" s="49"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A13" s="12">
         <v>12</v>
       </c>
@@ -1370,10 +1350,10 @@
       </c>
       <c r="J13" s="46"/>
       <c r="K13" s="46"/>
-      <c r="L13" s="50"/>
-      <c r="M13" s="47"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="L13" s="52"/>
+      <c r="M13" s="49"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A14" s="12">
         <v>13</v>
       </c>
@@ -1397,10 +1377,10 @@
       </c>
       <c r="J14" s="46"/>
       <c r="K14" s="46"/>
-      <c r="L14" s="50"/>
-      <c r="M14" s="47"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="L14" s="52"/>
+      <c r="M14" s="49"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A15" s="12">
         <v>14</v>
       </c>
@@ -1421,13 +1401,13 @@
         <v>7</v>
       </c>
       <c r="J15" s="46" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K15" s="46"/>
-      <c r="L15" s="50"/>
-      <c r="M15" s="47"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="L15" s="52"/>
+      <c r="M15" s="49"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A16" s="12">
         <v>15</v>
       </c>
@@ -1449,8 +1429,8 @@
       </c>
       <c r="J16" s="46"/>
       <c r="K16" s="46"/>
-      <c r="L16" s="50"/>
-      <c r="M16" s="47"/>
+      <c r="L16" s="52"/>
+      <c r="M16" s="49"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A17" s="12">
@@ -1474,8 +1454,8 @@
       </c>
       <c r="J17" s="46"/>
       <c r="K17" s="46"/>
-      <c r="L17" s="50"/>
-      <c r="M17" s="47"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="49"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A18" s="12">
@@ -1501,8 +1481,8 @@
       </c>
       <c r="J18" s="46"/>
       <c r="K18" s="46"/>
-      <c r="L18" s="50"/>
-      <c r="M18" s="47"/>
+      <c r="L18" s="52"/>
+      <c r="M18" s="49"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A19" s="16">
@@ -1519,18 +1499,18 @@
         <v>9</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I19" s="17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J19" s="41" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K19" s="46" t="s">
-        <v>92</v>
-      </c>
-      <c r="M19" s="47"/>
+        <v>94</v>
+      </c>
+      <c r="M19" s="49"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A20" s="16">
@@ -1547,16 +1527,16 @@
         <v>9</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J20" s="41" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K20" s="46"/>
-      <c r="M20" s="47"/>
+      <c r="M20" s="49"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A21" s="16">
@@ -1573,13 +1553,13 @@
         <v>9</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J21" s="41" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K21" s="46"/>
     </row>
@@ -1597,7 +1577,9 @@
       <c r="K22" s="46"/>
       <c r="L22" s="45"/>
       <c r="M22" s="45"/>
-      <c r="P22" s="20"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="5"/>
     </row>
     <row r="23" spans="1:16" s="19" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A23" s="45"/>
@@ -1613,7 +1595,9 @@
       <c r="K23" s="46"/>
       <c r="L23" s="45"/>
       <c r="M23" s="45"/>
-      <c r="P23" s="20"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="5"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A24" s="16">
@@ -1632,17 +1616,17 @@
         <v>9</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J24" s="46" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K24" s="46"/>
-      <c r="M24" s="47" t="s">
-        <v>98</v>
+      <c r="M24" s="49" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.4">
@@ -1660,14 +1644,14 @@
         <v>9</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I25" s="17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J25" s="46"/>
       <c r="K25" s="46"/>
-      <c r="M25" s="47"/>
+      <c r="M25" s="49"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A26" s="16">
@@ -1690,10 +1674,10 @@
         <v>40</v>
       </c>
       <c r="J26" s="46" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K26" s="46"/>
-      <c r="M26" s="47"/>
+      <c r="M26" s="49"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A27" s="16">
@@ -1717,7 +1701,7 @@
       </c>
       <c r="J27" s="46"/>
       <c r="K27" s="46"/>
-      <c r="M27" s="47"/>
+      <c r="M27" s="49"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A28" s="16">
@@ -1742,10 +1726,10 @@
         <v>41</v>
       </c>
       <c r="J28" s="46" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K28" s="46"/>
-      <c r="M28" s="47"/>
+      <c r="M28" s="49"/>
     </row>
     <row r="29" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="16">
@@ -1769,7 +1753,7 @@
       </c>
       <c r="J29" s="46"/>
       <c r="K29" s="46"/>
-      <c r="M29" s="47"/>
+      <c r="M29" s="49"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A30" s="16">
@@ -1792,11 +1776,11 @@
         <v>42</v>
       </c>
       <c r="J30" s="41" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K30" s="46"/>
       <c r="L30" s="44"/>
-      <c r="M30" s="47"/>
+      <c r="M30" s="49"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A31" s="16">
@@ -1816,14 +1800,14 @@
         <v>9</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J31" s="41" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K31" s="46"/>
       <c r="L31" s="44"/>
-      <c r="M31" s="47"/>
+      <c r="M31" s="49"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A32" s="21">
@@ -1847,16 +1831,16 @@
       <c r="I32" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="J32" s="52" t="s">
-        <v>94</v>
+      <c r="J32" s="48" t="s">
+        <v>96</v>
       </c>
       <c r="K32" s="46" t="s">
-        <v>86</v>
-      </c>
-      <c r="L32" s="51" t="s">
-        <v>49</v>
-      </c>
-      <c r="M32" s="47"/>
+        <v>88</v>
+      </c>
+      <c r="L32" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="M32" s="49"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A33" s="21">
@@ -1878,10 +1862,12 @@
       <c r="I33" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="J33" s="52"/>
+      <c r="J33" s="48"/>
       <c r="K33" s="46"/>
-      <c r="L33" s="51"/>
-      <c r="M33" s="47"/>
+      <c r="L33" s="53"/>
+      <c r="M33" s="49"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="2"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A34" s="21">
@@ -1904,11 +1890,13 @@
         <v>14</v>
       </c>
       <c r="J34" s="46" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K34" s="46"/>
-      <c r="L34" s="51"/>
-      <c r="M34" s="47"/>
+      <c r="L34" s="53"/>
+      <c r="M34" s="49"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="2"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A35" s="21">
@@ -1932,8 +1920,10 @@
       </c>
       <c r="J35" s="46"/>
       <c r="K35" s="46"/>
-      <c r="L35" s="51"/>
-      <c r="M35" s="47"/>
+      <c r="L35" s="53"/>
+      <c r="M35" s="49"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="2"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A36" s="21">
@@ -1961,8 +1951,8 @@
       </c>
       <c r="J36" s="46"/>
       <c r="K36" s="46"/>
-      <c r="L36" s="51"/>
-      <c r="M36" s="47"/>
+      <c r="L36" s="53"/>
+      <c r="M36" s="49"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A37" s="21">
@@ -1985,11 +1975,11 @@
         <v>43</v>
       </c>
       <c r="J37" s="41" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K37" s="46"/>
-      <c r="L37" s="51"/>
-      <c r="M37" s="47"/>
+      <c r="L37" s="53"/>
+      <c r="M37" s="49"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A38" s="21">
@@ -2012,11 +2002,11 @@
         <v>16</v>
       </c>
       <c r="J38" s="41" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K38" s="46"/>
-      <c r="L38" s="51"/>
-      <c r="M38" s="47"/>
+      <c r="L38" s="53"/>
+      <c r="M38" s="49"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A39" s="24">
@@ -2034,7 +2024,7 @@
         <v>18</v>
       </c>
       <c r="J39" s="41"/>
-      <c r="M39" s="47"/>
+      <c r="M39" s="49"/>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A40" s="24">
@@ -2054,7 +2044,7 @@
         <v>17</v>
       </c>
       <c r="J40" s="41"/>
-      <c r="M40" s="47"/>
+      <c r="M40" s="49"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A41" s="24">
@@ -2070,7 +2060,7 @@
       <c r="H41" s="26"/>
       <c r="I41" s="25"/>
       <c r="J41" s="41"/>
-      <c r="M41" s="47"/>
+      <c r="M41" s="49"/>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A42" s="24">
@@ -2086,7 +2076,7 @@
       <c r="H42" s="26"/>
       <c r="I42" s="25"/>
       <c r="J42" s="41"/>
-      <c r="M42" s="47"/>
+      <c r="M42" s="49"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A43" s="24">
@@ -2102,7 +2092,7 @@
       <c r="H43" s="26"/>
       <c r="I43" s="25"/>
       <c r="J43" s="41"/>
-      <c r="M43" s="47"/>
+      <c r="M43" s="49"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A44" s="39"/>
@@ -2124,11 +2114,11 @@
       <c r="H45" s="36"/>
       <c r="J45" s="41"/>
       <c r="K45" s="34" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="N45" s="3"/>
-      <c r="O45" s="3"/>
-      <c r="P45" s="3"/>
+      <c r="O45" s="4"/>
+      <c r="P45" s="5"/>
     </row>
     <row r="46" spans="1:16" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.4">
       <c r="B46" s="34"/>
@@ -2140,17 +2130,17 @@
         <v>8</v>
       </c>
       <c r="J46" s="43" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K46" s="35" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L46" s="37" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N46" s="3"/>
-      <c r="O46" s="3"/>
-      <c r="P46" s="3"/>
+      <c r="O46" s="4"/>
+      <c r="P46" s="5"/>
     </row>
     <row r="47" spans="1:16" s="2" customFormat="1" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B47" s="34"/>
@@ -2162,33 +2152,23 @@
         <v>3</v>
       </c>
       <c r="J47" s="43" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N47" s="3"/>
-      <c r="O47" s="3"/>
-      <c r="P47" s="3"/>
+      <c r="O47" s="4"/>
+      <c r="P47" s="5"/>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.4">
       <c r="I48" s="11" t="s">
         <v>9</v>
       </c>
       <c r="J48" s="43" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L48" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="J12:J14"/>
-    <mergeCell ref="J15:J18"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="J34:J36"/>
-    <mergeCell ref="K32:K38"/>
     <mergeCell ref="K2:K9"/>
     <mergeCell ref="K10:K18"/>
     <mergeCell ref="K19:K31"/>
@@ -2197,6 +2177,16 @@
     <mergeCell ref="L2:L9"/>
     <mergeCell ref="L10:L18"/>
     <mergeCell ref="L32:L38"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="J34:J36"/>
+    <mergeCell ref="K32:K38"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="J12:J14"/>
+    <mergeCell ref="J15:J18"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="J24:J25"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
